--- a/etf_holdings/2026-09-29_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:17</t>
+          <t>2026-09-29 01:01:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:17</t>
+          <t>2026-09-29 01:01:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:17</t>
+          <t>2026-09-29 01:01:08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:17</t>
+          <t>2026-09-29 01:01:08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:17</t>
+          <t>2026-09-29 01:01:08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:17</t>
+          <t>2026-09-29 01:01:08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:17</t>
+          <t>2026-09-29 01:01:08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:17</t>
+          <t>2026-09-29 01:01:08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:17</t>
+          <t>2026-09-29 01:01:08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:17</t>
+          <t>2026-09-29 01:01:08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:17</t>
+          <t>2026-09-29 01:01:08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:17</t>
+          <t>2026-09-29 01:01:08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:17</t>
+          <t>2026-09-29 01:01:08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:17</t>
+          <t>2026-09-29 01:01:08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:17</t>
+          <t>2026-09-29 01:01:08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:18</t>
+          <t>2026-09-29 01:01:10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:18</t>
+          <t>2026-09-29 01:01:10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:18</t>
+          <t>2026-09-29 01:01:10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:18</t>
+          <t>2026-09-29 01:01:10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:18</t>
+          <t>2026-09-29 01:01:10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:18</t>
+          <t>2026-09-29 01:01:10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:18</t>
+          <t>2026-09-29 01:01:10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:18</t>
+          <t>2026-09-29 01:01:10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:18</t>
+          <t>2026-09-29 01:01:10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:18</t>
+          <t>2026-09-29 01:01:10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:18</t>
+          <t>2026-09-29 01:01:10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:18</t>
+          <t>2026-09-29 01:01:10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:18</t>
+          <t>2026-09-29 01:01:10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:18</t>
+          <t>2026-09-29 01:01:10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:18</t>
+          <t>2026-09-29 01:01:10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:20</t>
+          <t>2026-09-29 01:01:11</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:20</t>
+          <t>2026-09-29 01:01:11</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:20</t>
+          <t>2026-09-29 01:01:11</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:20</t>
+          <t>2026-09-29 01:01:11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:20</t>
+          <t>2026-09-29 01:01:11</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:20</t>
+          <t>2026-09-29 01:01:11</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:20</t>
+          <t>2026-09-29 01:01:11</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:20</t>
+          <t>2026-09-29 01:01:11</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:20</t>
+          <t>2026-09-29 01:01:11</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:20</t>
+          <t>2026-09-29 01:01:11</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:20</t>
+          <t>2026-09-29 01:01:11</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:20</t>
+          <t>2026-09-29 01:01:11</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:20</t>
+          <t>2026-09-29 01:01:11</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:20</t>
+          <t>2026-09-29 01:01:11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:20</t>
+          <t>2026-09-29 01:01:11</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:21</t>
+          <t>2026-09-29 01:01:12</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:21</t>
+          <t>2026-09-29 01:01:12</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:21</t>
+          <t>2026-09-29 01:01:12</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:21</t>
+          <t>2026-09-29 01:01:12</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 00:52:21</t>
+          <t>2026-09-29 01:01:12</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-29_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:08</t>
+          <t>2026-09-29 01:39:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:08</t>
+          <t>2026-09-29 01:39:58</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:08</t>
+          <t>2026-09-29 01:39:58</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:08</t>
+          <t>2026-09-29 01:39:58</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:08</t>
+          <t>2026-09-29 01:39:58</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:08</t>
+          <t>2026-09-29 01:39:58</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:08</t>
+          <t>2026-09-29 01:39:58</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:08</t>
+          <t>2026-09-29 01:39:58</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:08</t>
+          <t>2026-09-29 01:39:58</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:08</t>
+          <t>2026-09-29 01:39:58</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:08</t>
+          <t>2026-09-29 01:39:58</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:08</t>
+          <t>2026-09-29 01:39:58</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:08</t>
+          <t>2026-09-29 01:39:58</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:08</t>
+          <t>2026-09-29 01:39:58</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:08</t>
+          <t>2026-09-29 01:39:58</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:10</t>
+          <t>2026-09-29 01:39:59</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:10</t>
+          <t>2026-09-29 01:39:59</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:10</t>
+          <t>2026-09-29 01:39:59</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:10</t>
+          <t>2026-09-29 01:39:59</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:10</t>
+          <t>2026-09-29 01:39:59</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:10</t>
+          <t>2026-09-29 01:39:59</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:10</t>
+          <t>2026-09-29 01:39:59</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:10</t>
+          <t>2026-09-29 01:39:59</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:10</t>
+          <t>2026-09-29 01:39:59</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:10</t>
+          <t>2026-09-29 01:39:59</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:10</t>
+          <t>2026-09-29 01:39:59</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:10</t>
+          <t>2026-09-29 01:39:59</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:10</t>
+          <t>2026-09-29 01:39:59</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:10</t>
+          <t>2026-09-29 01:39:59</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:10</t>
+          <t>2026-09-29 01:39:59</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:11</t>
+          <t>2026-09-29 01:40:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:11</t>
+          <t>2026-09-29 01:40:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:11</t>
+          <t>2026-09-29 01:40:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:11</t>
+          <t>2026-09-29 01:40:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:11</t>
+          <t>2026-09-29 01:40:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:11</t>
+          <t>2026-09-29 01:40:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:11</t>
+          <t>2026-09-29 01:40:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:11</t>
+          <t>2026-09-29 01:40:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:11</t>
+          <t>2026-09-29 01:40:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:11</t>
+          <t>2026-09-29 01:40:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:11</t>
+          <t>2026-09-29 01:40:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:11</t>
+          <t>2026-09-29 01:40:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:11</t>
+          <t>2026-09-29 01:40:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:11</t>
+          <t>2026-09-29 01:40:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:11</t>
+          <t>2026-09-29 01:40:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:12</t>
+          <t>2026-09-29 01:40:02</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:12</t>
+          <t>2026-09-29 01:40:02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:12</t>
+          <t>2026-09-29 01:40:02</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:12</t>
+          <t>2026-09-29 01:40:02</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:12</t>
+          <t>2026-09-29 01:40:02</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-29_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:58</t>
+          <t>2026-09-29 22:55:10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,12 +509,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1%2475</t>
+          <t>0%2475</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12.81%7,700,000</t>
+          <t>13.09%7,700,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>12.81%</t>
+          <t>13.09%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:58</t>
+          <t>2026-09-29 22:55:10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.93%5285</t>
+          <t>-7.1%4910</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+1.93%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5285</v>
+        <v>4910</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.85%2,210,000</t>
+          <t>7.45%2,210,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.85%</t>
+          <t>7.45%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:58</t>
+          <t>2026-09-29 22:55:10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+2.45%3555</t>
+          <t>-1.69%1165</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+2.45%</t>
+          <t>-1.69%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3555</v>
+        <v>1165</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.81%2,850,000</t>
+          <t>6.77%8,460,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.81%</t>
+          <t>6.77%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>2850000</v>
+        <v>8460000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:58</t>
+          <t>2026-09-29 22:55:10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+2.16%1185</t>
+          <t>-4.36%3400</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+2.16%</t>
+          <t>-4.36%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1185</v>
+        <v>3400</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.74%8,460,000</t>
+          <t>5.84%2,500,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.74%</t>
+          <t>5.84%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>8460000</v>
+        <v>2500000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:58</t>
+          <t>2026-09-29 22:55:10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-3.75%154</t>
+          <t>-0.32%153.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-3.75%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>154</v>
+        <v>153.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.38%52,000,000</t>
+          <t>5.48%52,000,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.38%</t>
+          <t>5.48%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:58</t>
+          <t>2026-09-29 22:55:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+7.96%6920</t>
+          <t>-0.36%6895</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+7.96%</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>6920</v>
+        <v>6895</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.19%1,115,000</t>
+          <t>5.28%1,115,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.19%</t>
+          <t>5.28%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:58</t>
+          <t>2026-09-29 22:55:10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+0.6%5050</t>
+          <t>-2.57%4920</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+0.6%</t>
+          <t>-2.57%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5050</v>
+        <v>4920</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.75%1,400,000</t>
+          <t>4.73%1,400,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.75%</t>
+          <t>4.73%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:58</t>
+          <t>2026-09-29 22:55:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-3.65%5415</t>
+          <t>-4.25%5185</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-3.65%</t>
+          <t>-4.25%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5415</v>
+        <v>5185</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.00%1,100,000</t>
+          <t>3.92%1,100,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.00%</t>
+          <t>3.92%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:58</t>
+          <t>2026-09-29 22:55:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+0.53%1910</t>
+          <t>-3.93%1835</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>-3.93%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1910</v>
+        <v>1835</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.72%2,900,000</t>
+          <t>3.66%2,900,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.72%</t>
+          <t>3.66%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:58</t>
+          <t>2026-09-29 22:55:10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,33 +1058,33 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+1.67%8525</t>
+          <t>-7.04%7925</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+1.67%</t>
+          <t>-7.04%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>8525</v>
+        <v>7925</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.70%646,000</t>
+          <t>3.32%610,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>3.32%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>646000</v>
+        <v>610000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:58</t>
+          <t>2026-09-29 22:55:10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+1.22%580</t>
+          <t>-5.52%548</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+1.22%</t>
+          <t>-5.52%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>580</v>
+        <v>548</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.12%8,000,000</t>
+          <t>3.01%8,000,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>3.01%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:58</t>
+          <t>2026-09-29 22:55:10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+6.18%962</t>
+          <t>-0.73%955</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+6.18%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>962</v>
+        <v>955</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.79%4,310,000</t>
+          <t>2.83%4,310,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>2.83%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:58</t>
+          <t>2026-09-29 22:55:10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+0.48%2115</t>
+          <t>-0.71%2100</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2115</v>
+        <v>2100</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.51%1,767,956</t>
+          <t>2.55%1,767,956</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>2.55%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:58</t>
+          <t>2026-09-29 22:55:10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+2.48%1240</t>
+          <t>+2.42%1270</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+2.48%</t>
+          <t>+2.42%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1240</v>
+        <v>1270</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.42%2,900,000</t>
+          <t>2.53%2,900,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>2.53%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:58</t>
+          <t>2026-09-29 22:55:10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,33 +1363,33 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+0.26%1895</t>
+          <t>-4.49%1810</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-4.49%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1895</v>
+        <v>1810</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.42%1,900,000</t>
+          <t>2.24%1,800,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>2.24%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>1900000</v>
+        <v>1800000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:59</t>
+          <t>2026-09-29 22:55:11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0%2340</t>
+          <t>+4.49%2445</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+4.49%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2340</v>
+        <v>2445</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.03%1,293,000</t>
+          <t>2.17%1,293,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>2.17%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:59</t>
+          <t>2026-09-29 22:55:11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,25 +1485,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+2.4%1495</t>
+          <t>-0.67%1485</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+2.4%</t>
+          <t>-0.67%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1495</v>
+        <v>1485</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.91%1,900,000</t>
+          <t>1.94%1,900,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.94%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:59</t>
+          <t>2026-09-29 22:55:11</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6488環球晶</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-0.21%948</t>
+          <t>+3.59%1585</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>+3.59%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>948</v>
+        <v>1585</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.78%2,800,000</t>
+          <t>1.85%1,700,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.85%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>2800000</v>
+        <v>1700000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:59</t>
+          <t>2026-09-29 22:55:11</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,34 +1602,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>6488環球晶</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-0.65%1530</t>
+          <t>-0.32%945</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-0.65%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1530</v>
+        <v>945</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.67%1,625,000</t>
+          <t>1.82%2,800,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.82%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>1625000</v>
+        <v>2800000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:59</t>
+          <t>2026-09-29 22:55:11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,25 +1668,25 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+4.62%238</t>
+          <t>+3.78%247</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+4.62%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.60%10,000,000</t>
+          <t>1.70%10,000,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.70%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:59</t>
+          <t>2026-09-29 22:55:11</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,25 +1729,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-2.69%2530</t>
+          <t>-0.59%2515</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-2.69%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2530</v>
+        <v>2515</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.43%840,000</t>
+          <t>1.45%840,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.45%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:59</t>
+          <t>2026-09-29 22:55:11</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,16 +1790,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-2.19%19835</t>
+          <t>-2.22%19395</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.22%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>19835</v>
+        <v>19395</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:59</t>
+          <t>2026-09-29 22:55:11</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,25 +1851,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+0.89%6245</t>
+          <t>-3.6%6020</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+0.89%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6245</v>
+        <v>6020</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.18%280,000</t>
+          <t>1.16%280,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.16%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:59</t>
+          <t>2026-09-29 22:55:11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,25 +1912,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-2.33%503</t>
+          <t>+0.6%506</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-2.33%</t>
+          <t>+0.6%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.95%2,800,000</t>
+          <t>0.97%2,800,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.97%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:59</t>
+          <t>2026-09-29 22:55:11</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,25 +1973,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+2.3%311</t>
+          <t>-5.31%294.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+2.3%</t>
+          <t>-5.31%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>311</v>
+        <v>294.5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.84%4,000,000</t>
+          <t>0.81%4,000,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:59</t>
+          <t>2026-09-29 22:55:11</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,16 +2034,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-0.32%12350</t>
+          <t>-1.9%12115</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>12350</v>
+        <v>12115</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:59</t>
+          <t>2026-09-29 22:55:11</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,12 +2095,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-2.15%250.5</t>
+          <t>0%250.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-2.15%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.54%3,200,000</t>
+          <t>0.55%3,200,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.55%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:59</t>
+          <t>2026-09-29 22:55:11</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,25 +2156,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-1.35%513</t>
+          <t>+2.34%525</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-1.35%</t>
+          <t>+2.34%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.52%1,500,000</t>
+          <t>0.54%1,500,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:59</t>
+          <t>2026-09-29 22:55:11</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,25 +2217,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-0.39%378.5</t>
+          <t>+1.98%386</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-0.39%</t>
+          <t>+1.98%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>378.5</v>
+        <v>386</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.51%2,000,000</t>
+          <t>0.53%2,000,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.53%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:59</t>
+          <t>2026-09-29 22:55:11</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>3583辛耘</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-1.29%2295</t>
+          <t>+2.15%713</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>+2.15%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>2295</v>
+        <v>713</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.48%310,000</t>
+          <t>0.39%800,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>310000</v>
+        <v>800000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:00</t>
+          <t>2026-09-29 22:55:12</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3583辛耘</t>
+          <t>6442光聖</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+1.01%698</t>
+          <t>-1.96%1500</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>698</v>
+        <v>1500</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.38%800,000</t>
+          <t>0.36%350,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>800000</v>
+        <v>350000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:00</t>
+          <t>2026-09-29 22:55:12</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,25 +2395,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6442光聖</t>
+          <t>2481強茂</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+0.99%1530</t>
+          <t>+0.57%175.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>+0.57%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1530</v>
+        <v>175.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.36%350,000</t>
+          <t>0.36%3,000,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>350000</v>
+        <v>3000000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:00</t>
+          <t>2026-09-29 22:55:12</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,34 +2456,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2481強茂</t>
+          <t>2882國泰金</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+0.87%174.5</t>
+          <t>+0.9%111.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+0.87%</t>
+          <t>+0.9%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>174.5</v>
+        <v>111.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.35%3,000,000</t>
+          <t>0.31%4,000,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>3000000</v>
+        <v>4000000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:00</t>
+          <t>2026-09-29 22:55:12</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2882國泰金</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-0.9%110.5</t>
+          <t>-4.79%2185</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-4.79%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>110.5</v>
+        <v>2185</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.30%4,000,000</t>
+          <t>0.21%140,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>4000000</v>
+        <v>140000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:00</t>
+          <t>2026-09-29 22:55:12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+0.36%554</t>
+          <t>-1.99%543</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>-1.99%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>554</v>
+        <v>543</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:00</t>
+          <t>2026-09-29 22:55:12</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,25 +2644,25 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+1.68%971</t>
+          <t>-1.54%956</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+1.68%</t>
+          <t>-1.54%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>971</v>
+        <v>956</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.12%191,000</t>
+          <t>0.13%191,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:00</t>
+          <t>2026-09-29 22:55:12</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+3.48%238</t>
+          <t>-2.31%232.5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+3.48%</t>
+          <t>-2.31%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>238</v>
+        <v>232.5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:00</t>
+          <t>2026-09-29 22:55:12</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+1.23%287</t>
+          <t>-2.09%281</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+1.23%</t>
+          <t>-2.09%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:00</t>
+          <t>2026-09-29 22:55:12</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+0.42%71.4</t>
+          <t>+1.54%72.5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>71.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:00</t>
+          <t>2026-09-29 22:55:12</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+2.82%511</t>
+          <t>-2.54%498</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>-2.54%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>511</v>
+        <v>498</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:00</t>
+          <t>2026-09-29 22:55:12</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-2.38%246</t>
+          <t>-1.83%241.5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-2.38%</t>
+          <t>-1.83%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>246</v>
+        <v>241.5</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:00</t>
+          <t>2026-09-29 22:55:12</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-1.68%117</t>
+          <t>+1.28%118.5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-1.68%</t>
+          <t>+1.28%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>117</v>
+        <v>118.5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:00</t>
+          <t>2026-09-29 22:55:12</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-4.06%2125</t>
+          <t>-0.47%2115</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-4.06%</t>
+          <t>-0.47%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>2125</v>
+        <v>2115</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:00</t>
+          <t>2026-09-29 22:55:12</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+2.91%565</t>
+          <t>-3.72%544</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+2.91%</t>
+          <t>-3.72%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>565</v>
+        <v>544</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:00</t>
+          <t>2026-09-29 22:55:12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+0.17%287</t>
+          <t>-2.09%281</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-2.09%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:02</t>
+          <t>2026-09-29 22:55:13</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,16 +3254,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+0.62%325.5</t>
+          <t>+3.07%335.5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+0.62%</t>
+          <t>+3.07%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>325.5</v>
+        <v>335.5</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:02</t>
+          <t>2026-09-29 22:55:13</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+2.8%1285</t>
+          <t>-5.06%1220</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+2.8%</t>
+          <t>-5.06%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1285</v>
+        <v>1220</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:02</t>
+          <t>2026-09-29 22:55:13</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-5.1%5670</t>
+          <t>-1.5%5585</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>5670</v>
+        <v>5585</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:02</t>
+          <t>2026-09-29 22:55:13</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-0.58%171.5</t>
+          <t>+1.46%174</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-0.58%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>171.5</v>
+        <v>174</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:02</t>
+          <t>2026-09-29 22:55:13</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+0.87%699</t>
+          <t>-1.72%687</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+0.87%</t>
+          <t>-1.72%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>699</v>
+        <v>687</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-09-29_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:10</t>
+          <t>2026-09-29 23:06:29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:10</t>
+          <t>2026-09-29 23:06:29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:10</t>
+          <t>2026-09-29 23:06:29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:10</t>
+          <t>2026-09-29 23:06:29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:10</t>
+          <t>2026-09-29 23:06:29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:10</t>
+          <t>2026-09-29 23:06:29</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:10</t>
+          <t>2026-09-29 23:06:29</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:10</t>
+          <t>2026-09-29 23:06:29</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:10</t>
+          <t>2026-09-29 23:06:29</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:10</t>
+          <t>2026-09-29 23:06:29</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:10</t>
+          <t>2026-09-29 23:06:29</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:10</t>
+          <t>2026-09-29 23:06:29</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:10</t>
+          <t>2026-09-29 23:06:29</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:10</t>
+          <t>2026-09-29 23:06:29</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:10</t>
+          <t>2026-09-29 23:06:29</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:11</t>
+          <t>2026-09-29 23:06:31</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:11</t>
+          <t>2026-09-29 23:06:31</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:11</t>
+          <t>2026-09-29 23:06:31</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:11</t>
+          <t>2026-09-29 23:06:31</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:11</t>
+          <t>2026-09-29 23:06:31</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:11</t>
+          <t>2026-09-29 23:06:31</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:11</t>
+          <t>2026-09-29 23:06:31</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:11</t>
+          <t>2026-09-29 23:06:31</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:11</t>
+          <t>2026-09-29 23:06:31</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:11</t>
+          <t>2026-09-29 23:06:31</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:11</t>
+          <t>2026-09-29 23:06:31</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:11</t>
+          <t>2026-09-29 23:06:31</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:11</t>
+          <t>2026-09-29 23:06:31</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:11</t>
+          <t>2026-09-29 23:06:31</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:11</t>
+          <t>2026-09-29 23:06:31</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:12</t>
+          <t>2026-09-29 23:06:32</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:12</t>
+          <t>2026-09-29 23:06:32</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:12</t>
+          <t>2026-09-29 23:06:32</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:12</t>
+          <t>2026-09-29 23:06:32</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:12</t>
+          <t>2026-09-29 23:06:32</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:12</t>
+          <t>2026-09-29 23:06:32</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:12</t>
+          <t>2026-09-29 23:06:32</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:12</t>
+          <t>2026-09-29 23:06:32</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:12</t>
+          <t>2026-09-29 23:06:32</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:12</t>
+          <t>2026-09-29 23:06:32</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:12</t>
+          <t>2026-09-29 23:06:32</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:12</t>
+          <t>2026-09-29 23:06:32</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:12</t>
+          <t>2026-09-29 23:06:32</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:12</t>
+          <t>2026-09-29 23:06:32</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:12</t>
+          <t>2026-09-29 23:06:32</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:13</t>
+          <t>2026-09-29 23:06:34</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:13</t>
+          <t>2026-09-29 23:06:34</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:13</t>
+          <t>2026-09-29 23:06:34</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:13</t>
+          <t>2026-09-29 23:06:34</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 22:55:13</t>
+          <t>2026-09-29 23:06:34</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-29_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:29</t>
+          <t>2026-09-29 23:50:46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:29</t>
+          <t>2026-09-29 23:50:46</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:29</t>
+          <t>2026-09-29 23:50:46</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:29</t>
+          <t>2026-09-29 23:50:46</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:29</t>
+          <t>2026-09-29 23:50:46</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:29</t>
+          <t>2026-09-29 23:50:46</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:29</t>
+          <t>2026-09-29 23:50:46</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:29</t>
+          <t>2026-09-29 23:50:46</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:29</t>
+          <t>2026-09-29 23:50:46</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:29</t>
+          <t>2026-09-29 23:50:46</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:29</t>
+          <t>2026-09-29 23:50:46</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:29</t>
+          <t>2026-09-29 23:50:46</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:29</t>
+          <t>2026-09-29 23:50:46</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:29</t>
+          <t>2026-09-29 23:50:46</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:29</t>
+          <t>2026-09-29 23:50:46</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:31</t>
+          <t>2026-09-29 23:50:47</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:31</t>
+          <t>2026-09-29 23:50:47</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:31</t>
+          <t>2026-09-29 23:50:47</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:31</t>
+          <t>2026-09-29 23:50:47</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:31</t>
+          <t>2026-09-29 23:50:47</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:31</t>
+          <t>2026-09-29 23:50:47</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:31</t>
+          <t>2026-09-29 23:50:47</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:31</t>
+          <t>2026-09-29 23:50:47</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:31</t>
+          <t>2026-09-29 23:50:47</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:31</t>
+          <t>2026-09-29 23:50:47</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:31</t>
+          <t>2026-09-29 23:50:47</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:31</t>
+          <t>2026-09-29 23:50:47</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:31</t>
+          <t>2026-09-29 23:50:47</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:31</t>
+          <t>2026-09-29 23:50:47</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:31</t>
+          <t>2026-09-29 23:50:47</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:32</t>
+          <t>2026-09-29 23:50:48</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:32</t>
+          <t>2026-09-29 23:50:48</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:32</t>
+          <t>2026-09-29 23:50:48</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:32</t>
+          <t>2026-09-29 23:50:48</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:32</t>
+          <t>2026-09-29 23:50:48</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:32</t>
+          <t>2026-09-29 23:50:48</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:32</t>
+          <t>2026-09-29 23:50:48</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:32</t>
+          <t>2026-09-29 23:50:48</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:32</t>
+          <t>2026-09-29 23:50:48</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:32</t>
+          <t>2026-09-29 23:50:48</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:32</t>
+          <t>2026-09-29 23:50:48</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:32</t>
+          <t>2026-09-29 23:50:48</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:32</t>
+          <t>2026-09-29 23:50:48</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:32</t>
+          <t>2026-09-29 23:50:48</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:32</t>
+          <t>2026-09-29 23:50:48</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:34</t>
+          <t>2026-09-29 23:50:50</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:34</t>
+          <t>2026-09-29 23:50:50</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:34</t>
+          <t>2026-09-29 23:50:50</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:34</t>
+          <t>2026-09-29 23:50:50</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 23:06:34</t>
+          <t>2026-09-29 23:50:50</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
